--- a/product-updates/Court_Ready_Master_Index_SAMPLE.xlsx
+++ b/product-updates/Court_Ready_Master_Index_SAMPLE.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>2026-07-18_Screenshot_EVT-0001_ExA.png</t>
+          <t>EVT-0001_2026-07-18_Exchange_ExA_Screenshot.png</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>2026-07-19_Document_EVT-0002_ExA.pdf</t>
+          <t>EVT-0002_2026-07-19_Medical_ExA_Document.pdf</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>2026-07-24_Screenshot_EVT-0003_ExA.png</t>
+          <t>EVT-0003_2026-07-24_Communication_ExA_Screenshot.png</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>2026-08-01_Photo_EVT-0005_ExA.png</t>
+          <t>EVT-0005_2026-08-01_Exchange_ExA_Photo.png</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>2026-08-05_Document_EVT-0006_ExA.pdf</t>
+          <t>EVT-0006_2026-08-05_School_ExA_Document.pdf</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>2026-08-08_Receipt_EVT-0007_ExA.pdf</t>
+          <t>EVT-0007_2026-08-08_Expense_ExA_Receipt.pdf</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>2026-08-12_Screenshot_EVT-0008_ExA.png</t>
+          <t>EVT-0008_2026-08-12_Incident_ExA_Screenshot.png</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
